--- a/OperationGuidance_new/OperationDataStorage/test.xlsx
+++ b/OperationGuidance_new/OperationDataStorage/test.xlsx
@@ -1,29 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<x:workbook xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<x:workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:workbookPr codeName="ThisWorkbook"/>
   <x:bookViews>
-    <x:workbookView windowWidth="27810" windowHeight="12975" firstSheet="0" activeTab="0"/>
+    <x:workbookView firstSheet="0" activeTab="0"/>
   </x:bookViews>
   <x:sheets>
-    <x:sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <x:sheet name="Sheet1" sheetId="1" r:id="rId2"/>
   </x:sheets>
   <x:definedNames/>
-  <x:calcPr calcId="191029"/>
-  <x:extLst>
-    <x:ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </x:ext>
-  </x:extLst>
+  <x:calcPr calcId="125725"/>
 </x:workbook>
 </file>
 
@@ -264,756 +250,127 @@
     <x:t>modify_time</x:t>
   </x:si>
   <x:si>
+    <x:t>一号站点</x:t>
+  </x:si>
+  <x:si>
+    <x:t>工具1号</x:t>
+  </x:si>
+  <x:si>
+    <x:t>192.168.1.11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PF4000</x:t>
+  </x:si>
+  <x:si>
     <x:t xml:space="preserve">                         </x:t>
   </x:si>
   <x:si>
     <x:t>00000004750413</x:t>
   </x:si>
   <x:si>
-    <x:t>1990-01-01:16:42:39</x:t>
+    <x:t>1990-01-01:00:44:06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1990-01-01:00:05:52</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">             cw2000degree</x:t>
+  </x:si>
+  <x:si>
+    <x:t>超级管理员</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1990-01-01:00:44:07</x:t>
   </x:si>
   <x:si>
     <x:t>1990-01-01:06:34:30</x:t>
   </x:si>
   <x:si>
-    <x:t>Admin</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1990-01-01:16:42:40</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1990-01-01:16:42:41</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1990-01-01:00:05:52</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">             cw2000degree</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1990-01-01:16:42:43</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1990-01-01:16:48:12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1990-01-01:16:48:13</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1990-01-01:16:48:14</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1990-01-01:16:48:15</x:t>
-  </x:si>
-  <x:si>
-    <x:t>一号站点</x:t>
-  </x:si>
-  <x:si>
-    <x:t>工具1号</x:t>
-  </x:si>
-  <x:si>
-    <x:t>192.168.1.11</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PF4000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1990-01-01:17:05:17</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1990-01-01:17:05:18</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1990-01-01:17:05:19</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1990-01-01:17:05:21</x:t>
+    <x:t>1990-01-01:00:44:09</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1990-01-01:06:35:23</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">                       33</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1990-01-01:00:44:11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1990-01-01:00:44:13</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1990-01-01:00:44:15</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1990-01-01:00:44:18</x:t>
   </x:si>
 </x:sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<x:styleSheet xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="xr9">
-  <x:numFmts count="4">
-    <x:numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <x:numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <x:numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <x:numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+<x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:numFmts count="1">
+    <x:numFmt numFmtId="0" formatCode=""/>
   </x:numFmts>
-  <x:fonts count="21">
+  <x:fonts count="1">
     <x:font>
+      <x:vertAlign val="baseline"/>
       <x:sz val="11"/>
       <x:color rgb="FF000000"/>
       <x:name val="Calibri"/>
-      <x:charset val="134"/>
-    </x:font>
-    <x:font>
-      <x:sz val="11"/>
-      <x:color theme="1"/>
-      <x:name val="宋体"/>
-      <x:charset val="134"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:u/>
-      <x:sz val="11"/>
-      <x:color rgb="FF0000FF"/>
-      <x:name val="宋体"/>
-      <x:charset val="0"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:u/>
-      <x:sz val="11"/>
-      <x:color rgb="FF800080"/>
-      <x:name val="宋体"/>
-      <x:charset val="0"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:sz val="11"/>
-      <x:color rgb="FFFF0000"/>
-      <x:name val="宋体"/>
-      <x:charset val="0"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="18"/>
-      <x:color theme="3"/>
-      <x:name val="宋体"/>
-      <x:charset val="134"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:i/>
-      <x:sz val="11"/>
-      <x:color rgb="FF7F7F7F"/>
-      <x:name val="宋体"/>
-      <x:charset val="0"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="15"/>
-      <x:color theme="3"/>
-      <x:name val="宋体"/>
-      <x:charset val="134"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="13"/>
-      <x:color theme="3"/>
-      <x:name val="宋体"/>
-      <x:charset val="134"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="11"/>
-      <x:color theme="3"/>
-      <x:name val="宋体"/>
-      <x:charset val="134"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:sz val="11"/>
-      <x:color rgb="FF3F3F76"/>
-      <x:name val="宋体"/>
-      <x:charset val="0"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="11"/>
-      <x:color rgb="FF3F3F3F"/>
-      <x:name val="宋体"/>
-      <x:charset val="0"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="11"/>
-      <x:color rgb="FFFA7D00"/>
-      <x:name val="宋体"/>
-      <x:charset val="0"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="11"/>
-      <x:color rgb="FFFFFFFF"/>
-      <x:name val="宋体"/>
-      <x:charset val="0"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:sz val="11"/>
-      <x:color rgb="FFFA7D00"/>
-      <x:name val="宋体"/>
-      <x:charset val="0"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="11"/>
-      <x:color theme="1"/>
-      <x:name val="宋体"/>
-      <x:charset val="0"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:sz val="11"/>
-      <x:color rgb="FF006100"/>
-      <x:name val="宋体"/>
-      <x:charset val="0"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:sz val="11"/>
-      <x:color rgb="FF9C0006"/>
-      <x:name val="宋体"/>
-      <x:charset val="0"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:sz val="11"/>
-      <x:color rgb="FF9C6500"/>
-      <x:name val="宋体"/>
-      <x:charset val="0"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:sz val="11"/>
-      <x:color theme="0"/>
-      <x:name val="宋体"/>
-      <x:charset val="0"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:sz val="11"/>
-      <x:color theme="1"/>
-      <x:name val="宋体"/>
-      <x:charset val="0"/>
-      <x:scheme val="minor"/>
+      <x:family val="2"/>
     </x:font>
   </x:fonts>
-  <x:fills count="33">
+  <x:fills count="2">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="gray125"/>
     </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFFFFFCC"/>
-        <x:bgColor indexed="64"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFFFCC99"/>
-        <x:bgColor indexed="64"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFF2F2F2"/>
-        <x:bgColor indexed="64"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFA5A5A5"/>
-        <x:bgColor indexed="64"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFC6EFCE"/>
-        <x:bgColor indexed="64"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFFFC7CE"/>
-        <x:bgColor indexed="64"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFFFEB9C"/>
-        <x:bgColor indexed="64"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="4"/>
-        <x:bgColor indexed="64"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="4" tint="0.799981688894314"/>
-        <x:bgColor indexed="64"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="4" tint="0.599993896298105"/>
-        <x:bgColor indexed="64"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="4" tint="0.399975585192419"/>
-        <x:bgColor indexed="64"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="5"/>
-        <x:bgColor indexed="64"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="5" tint="0.799981688894314"/>
-        <x:bgColor indexed="64"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="5" tint="0.599993896298105"/>
-        <x:bgColor indexed="64"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="5" tint="0.399975585192419"/>
-        <x:bgColor indexed="64"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="6"/>
-        <x:bgColor indexed="64"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="6" tint="0.799981688894314"/>
-        <x:bgColor indexed="64"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="6" tint="0.599993896298105"/>
-        <x:bgColor indexed="64"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="6" tint="0.399975585192419"/>
-        <x:bgColor indexed="64"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="7"/>
-        <x:bgColor indexed="64"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="7" tint="0.799981688894314"/>
-        <x:bgColor indexed="64"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="7" tint="0.599993896298105"/>
-        <x:bgColor indexed="64"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="7" tint="0.399975585192419"/>
-        <x:bgColor indexed="64"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="8"/>
-        <x:bgColor indexed="64"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="8" tint="0.799981688894314"/>
-        <x:bgColor indexed="64"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="8" tint="0.599993896298105"/>
-        <x:bgColor indexed="64"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="8" tint="0.399975585192419"/>
-        <x:bgColor indexed="64"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="9"/>
-        <x:bgColor indexed="64"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="9" tint="0.799981688894314"/>
-        <x:bgColor indexed="64"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="9" tint="0.599993896298105"/>
-        <x:bgColor indexed="64"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="9" tint="0.399975585192419"/>
-        <x:bgColor indexed="64"/>
-      </x:patternFill>
-    </x:fill>
   </x:fills>
-  <x:borders count="9">
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-      <x:diagonal/>
-    </x:border>
-    <x:border>
-      <x:left style="thin">
-        <x:color rgb="FFB2B2B2"/>
+  <x:borders count="1">
+    <x:border diagonalUp="0" diagonalDown="0">
+      <x:left style="none">
+        <x:color rgb="FF000000"/>
       </x:left>
-      <x:right style="thin">
-        <x:color rgb="FFB2B2B2"/>
+      <x:right style="none">
+        <x:color rgb="FF000000"/>
       </x:right>
-      <x:top style="thin">
-        <x:color rgb="FFB2B2B2"/>
+      <x:top style="none">
+        <x:color rgb="FF000000"/>
       </x:top>
-      <x:bottom style="thin">
-        <x:color rgb="FFB2B2B2"/>
+      <x:bottom style="none">
+        <x:color rgb="FF000000"/>
       </x:bottom>
-      <x:diagonal/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom style="medium">
-        <x:color theme="4"/>
-      </x:bottom>
-      <x:diagonal/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom style="medium">
-        <x:color theme="4" tint="0.499984740745262"/>
-      </x:bottom>
-      <x:diagonal/>
-    </x:border>
-    <x:border>
-      <x:left style="thin">
-        <x:color rgb="FF7F7F7F"/>
-      </x:left>
-      <x:right style="thin">
-        <x:color rgb="FF7F7F7F"/>
-      </x:right>
-      <x:top style="thin">
-        <x:color rgb="FF7F7F7F"/>
-      </x:top>
-      <x:bottom style="thin">
-        <x:color rgb="FF7F7F7F"/>
-      </x:bottom>
-      <x:diagonal/>
-    </x:border>
-    <x:border>
-      <x:left style="thin">
-        <x:color rgb="FF3F3F3F"/>
-      </x:left>
-      <x:right style="thin">
-        <x:color rgb="FF3F3F3F"/>
-      </x:right>
-      <x:top style="thin">
-        <x:color rgb="FF3F3F3F"/>
-      </x:top>
-      <x:bottom style="thin">
-        <x:color rgb="FF3F3F3F"/>
-      </x:bottom>
-      <x:diagonal/>
-    </x:border>
-    <x:border>
-      <x:left style="double">
-        <x:color rgb="FF3F3F3F"/>
-      </x:left>
-      <x:right style="double">
-        <x:color rgb="FF3F3F3F"/>
-      </x:right>
-      <x:top style="double">
-        <x:color rgb="FF3F3F3F"/>
-      </x:top>
-      <x:bottom style="double">
-        <x:color rgb="FF3F3F3F"/>
-      </x:bottom>
-      <x:diagonal/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom style="double">
-        <x:color rgb="FFFF8001"/>
-      </x:bottom>
-      <x:diagonal/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top style="thin">
-        <x:color theme="4"/>
-      </x:top>
-      <x:bottom style="double">
-        <x:color theme="4"/>
-      </x:bottom>
-      <x:diagonal/>
+      <x:diagonal style="none">
+        <x:color rgb="FF000000"/>
+      </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="50">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyBorder="0"/>
-    <x:xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <x:alignment vertical="center"/>
+  <x:cellStyleXfs count="2">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="22" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
   <x:cellXfs count="2">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
-    <x:xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
   </x:cellXfs>
-  <x:cellStyles count="49">
-    <x:cellStyle name="常规" xfId="0" builtinId="0"/>
-    <x:cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <x:cellStyle name="货币" xfId="2" builtinId="4"/>
-    <x:cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <x:cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <x:cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <x:cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <x:cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <x:cellStyle name="注释" xfId="8" builtinId="10"/>
-    <x:cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <x:cellStyle name="标题" xfId="10" builtinId="15"/>
-    <x:cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <x:cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <x:cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <x:cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <x:cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <x:cellStyle name="输入" xfId="16" builtinId="20"/>
-    <x:cellStyle name="输出" xfId="17" builtinId="21"/>
-    <x:cellStyle name="计算" xfId="18" builtinId="22"/>
-    <x:cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <x:cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <x:cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <x:cellStyle name="好" xfId="22" builtinId="26"/>
-    <x:cellStyle name="差" xfId="23" builtinId="27"/>
-    <x:cellStyle name="适中" xfId="24" builtinId="28"/>
-    <x:cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <x:cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <x:cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <x:cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <x:cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <x:cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <x:cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <x:cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <x:cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <x:cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <x:cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <x:cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <x:cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <x:cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <x:cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <x:cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <x:cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <x:cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <x:cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <x:cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <x:cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <x:cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <x:cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <x:cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+  <x:cellStyles count="1">
+    <x:cellStyle name="Normal" xfId="0" builtinId="0"/>
   </x:cellStyles>
-  <x:tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1 1" defaultPivotStyle="PivotStylePreset2_Accent1 1">
-    <x:tableStyle name="TableStylePreset3_Accent1 1" pivot="0" count="0" xr9:uid="{B79B40E5-C4C5-48C5-9DB4-24982918F348}"/>
-    <x:tableStyle name="PivotStylePreset2_Accent1 1" table="0" count="0" xr9:uid="{F41D137F-167E-43D5-8327-E9CB947592F6}"/>
-  </x:tableStyles>
-  <x:extLst>
-    <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </x:ext>
-  </x:extLst>
 </x:styleSheet>
 </file>
 
@@ -1296,94 +653,17 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:BZ13"/>
-  <x:sheetFormatPr defaultColWidth="8.996339" defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="1" width="15.428571" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="19.142857" style="0" customWidth="1"/>
-    <x:col min="3" max="3" width="11.285714" style="0" customWidth="1"/>
-    <x:col min="4" max="4" width="12.571429" style="0" customWidth="1"/>
-    <x:col min="5" max="5" width="10.142857" style="0" customWidth="1"/>
-    <x:col min="6" max="6" width="9.857143" style="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16.571429" style="0" customWidth="1"/>
-    <x:col min="8" max="8" width="16.714286" style="0" customWidth="1"/>
-    <x:col min="9" max="9" width="17.571429" style="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15.428571" style="0" customWidth="1"/>
-    <x:col min="11" max="12" width="19.142857" style="0" customWidth="1"/>
-    <x:col min="13" max="13" width="17.428571" style="0" customWidth="1"/>
-    <x:col min="14" max="14" width="19.428571" style="0" customWidth="1"/>
-    <x:col min="15" max="15" width="21.285714" style="0" customWidth="1"/>
-    <x:col min="16" max="16" width="7.428571" style="0" customWidth="1"/>
-    <x:col min="17" max="17" width="11.428571" style="0" customWidth="1"/>
-    <x:col min="18" max="18" width="25" style="0" customWidth="1"/>
-    <x:col min="19" max="19" width="12.571429" style="0" customWidth="1"/>
-    <x:col min="20" max="20" width="7.142857" style="0" customWidth="1"/>
-    <x:col min="21" max="21" width="24.142857" style="0" customWidth="1"/>
-    <x:col min="22" max="22" width="8.714286" style="0" customWidth="1"/>
-    <x:col min="23" max="23" width="17.285714" style="0" customWidth="1"/>
-    <x:col min="24" max="24" width="11" style="0" customWidth="1"/>
-    <x:col min="25" max="25" width="14.857143" style="0" customWidth="1"/>
-    <x:col min="26" max="26" width="17.857143" style="0" customWidth="1"/>
-    <x:col min="27" max="27" width="13" style="0" customWidth="1"/>
-    <x:col min="28" max="28" width="14.285714" style="0" customWidth="1"/>
-    <x:col min="29" max="29" width="13" style="0" customWidth="1"/>
-    <x:col min="30" max="30" width="16.571429" style="0" customWidth="1"/>
-    <x:col min="31" max="31" width="24.428571" style="0" customWidth="1"/>
-    <x:col min="32" max="32" width="23.142857" style="0" customWidth="1"/>
-    <x:col min="33" max="33" width="27" style="0" customWidth="1"/>
-    <x:col min="34" max="34" width="15.571429" style="0" customWidth="1"/>
-    <x:col min="35" max="35" width="34.571429" style="0" customWidth="1"/>
-    <x:col min="36" max="36" width="35.714286" style="0" customWidth="1"/>
-    <x:col min="37" max="37" width="24" style="0" customWidth="1"/>
-    <x:col min="38" max="38" width="18" style="0" customWidth="1"/>
-    <x:col min="39" max="39" width="18.285714" style="0" customWidth="1"/>
-    <x:col min="40" max="40" width="20" style="0" customWidth="1"/>
-    <x:col min="41" max="41" width="12.857143" style="0" customWidth="1"/>
-    <x:col min="42" max="42" width="11" style="0" customWidth="1"/>
-    <x:col min="43" max="43" width="11.285714" style="0" customWidth="1"/>
-    <x:col min="44" max="44" width="18.714286" style="0" customWidth="1"/>
-    <x:col min="45" max="45" width="6.428571" style="0" customWidth="1"/>
-    <x:col min="46" max="46" width="21.142857" style="0" customWidth="1"/>
-    <x:col min="47" max="47" width="21.428571" style="0" customWidth="1"/>
-    <x:col min="48" max="48" width="16.142857" style="0" customWidth="1"/>
-    <x:col min="49" max="49" width="23.142857" style="0" customWidth="1"/>
-    <x:col min="50" max="50" width="22.428571" style="0" customWidth="1"/>
-    <x:col min="51" max="51" width="22.714286" style="0" customWidth="1"/>
-    <x:col min="52" max="52" width="17.428571" style="0" customWidth="1"/>
-    <x:col min="53" max="53" width="24.428571" style="0" customWidth="1"/>
-    <x:col min="54" max="54" width="25" style="0" customWidth="1"/>
-    <x:col min="55" max="55" width="25.285714" style="0" customWidth="1"/>
-    <x:col min="56" max="56" width="26.571429" style="0" customWidth="1"/>
-    <x:col min="57" max="57" width="13.571429" style="0" customWidth="1"/>
-    <x:col min="58" max="58" width="13.857143" style="0" customWidth="1"/>
-    <x:col min="59" max="59" width="16.428571" style="0" customWidth="1"/>
-    <x:col min="60" max="60" width="32.428571" style="0" customWidth="1"/>
-    <x:col min="61" max="61" width="32.857143" style="0" customWidth="1"/>
-    <x:col min="62" max="62" width="15.285714" style="0" customWidth="1"/>
-    <x:col min="63" max="63" width="13.857143" style="0" customWidth="1"/>
-    <x:col min="64" max="64" width="23.428571" style="0" customWidth="1"/>
-    <x:col min="65" max="65" width="19.285714" style="0" customWidth="1"/>
-    <x:col min="66" max="66" width="20.142857" style="0" customWidth="1"/>
-    <x:col min="67" max="67" width="19.857143" style="0" customWidth="1"/>
-    <x:col min="68" max="68" width="57.857143" style="0" customWidth="1"/>
-    <x:col min="69" max="69" width="21.857143" style="0" customWidth="1"/>
-    <x:col min="70" max="70" width="20" style="0" customWidth="1"/>
-    <x:col min="71" max="71" width="11.857143" style="0" customWidth="1"/>
-    <x:col min="72" max="72" width="3.571429" style="0" customWidth="1"/>
-    <x:col min="73" max="73" width="8.142857" style="0" customWidth="1"/>
-    <x:col min="74" max="74" width="8.571429" style="0" customWidth="1"/>
-    <x:col min="75" max="75" width="7.857143" style="0" customWidth="1"/>
-    <x:col min="76" max="76" width="9.285714" style="0" customWidth="1"/>
-    <x:col min="77" max="78" width="13.714286" style="0" customWidth="1"/>
-  </x:cols>
+  <x:dimension ref="A1:BZ8"/>
+  <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:78">
       <x:c r="A1" s="0" t="s">
@@ -1622,6 +902,27 @@
       </x:c>
     </x:row>
     <x:row r="2" spans="1:78">
+      <x:c r="A2" s="0">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B2" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="C2" s="0" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="D2" s="0" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="E2" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="G2" s="0">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="H2" s="0">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="P2" s="0">
         <x:v>0</x:v>
       </x:c>
@@ -1629,16 +930,16 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="R2" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="S2" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="T2" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="U2" s="0">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="V2" s="0">
         <x:v>10</x:v>
@@ -1695,7 +996,7 @@
         <x:v>9999</x:v>
       </x:c>
       <x:c r="AO2" s="0">
-        <x:v>0.119999997317791</x:v>
+        <x:v>0.129999995231628</x:v>
       </x:c>
       <x:c r="AP2" s="0">
         <x:v>1800</x:v>
@@ -1743,7 +1044,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="BE2" s="0">
-        <x:v>1.64999997615814</x:v>
+        <x:v>0.300000011920929</x:v>
       </x:c>
       <x:c r="BF2" s="0">
         <x:v>9999</x:v>
@@ -1752,16 +1053,16 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="BH2" s="0">
-        <x:v>1.64999997615814</x:v>
+        <x:v>0.300000011920929</x:v>
       </x:c>
       <x:c r="BI2" s="0">
-        <x:v>11</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="BJ2" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="BK2" s="0">
-        <x:v>1827</x:v>
+        <x:v>1843</x:v>
       </x:c>
       <x:c r="BL2" s="0">
         <x:v>0</x:v>
@@ -1770,16 +1071,16 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="BN2" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="BO2" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="BP2" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="BQ2" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="BR2" s="0">
         <x:v>1</x:v>
@@ -1797,19 +1098,40 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="BW2" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="BX2" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="BY2" s="1">
-        <x:v>45329.0995294676</x:v>
+        <x:v>45329.4401879167</x:v>
       </x:c>
       <x:c r="BZ2" s="1">
-        <x:v>45329.0995294676</x:v>
+        <x:v>45329.4401879167</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:78">
+      <x:c r="A3" s="0">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B3" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="C3" s="0" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="D3" s="0" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="E3" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="G3" s="0">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="H3" s="0">
+        <x:v>2</x:v>
+      </x:c>
       <x:c r="P3" s="0">
         <x:v>0</x:v>
       </x:c>
@@ -1817,10 +1139,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="R3" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="S3" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="T3" s="0">
         <x:v>0</x:v>
@@ -1883,7 +1205,7 @@
         <x:v>9999</x:v>
       </x:c>
       <x:c r="AO3" s="0">
-        <x:v>0.119999997317791</x:v>
+        <x:v>0.140000000596046</x:v>
       </x:c>
       <x:c r="AP3" s="0">
         <x:v>1800</x:v>
@@ -1949,7 +1271,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="BK3" s="0">
-        <x:v>1828</x:v>
+        <x:v>1844</x:v>
       </x:c>
       <x:c r="BL3" s="0">
         <x:v>0</x:v>
@@ -1958,16 +1280,16 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="BN3" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="BO3" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="BP3" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="BQ3" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="BR3" s="0">
         <x:v>1</x:v>
@@ -1985,19 +1307,40 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="BW3" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="BX3" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="BY3" s="1">
-        <x:v>45329.0995440625</x:v>
+        <x:v>45329.44020625</x:v>
       </x:c>
       <x:c r="BZ3" s="1">
-        <x:v>45329.0995440625</x:v>
+        <x:v>45329.44020625</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:78">
+      <x:c r="A4" s="0">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B4" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="C4" s="0" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="D4" s="0" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="E4" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="G4" s="0">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="H4" s="0">
+        <x:v>3</x:v>
+      </x:c>
       <x:c r="P4" s="0">
         <x:v>0</x:v>
       </x:c>
@@ -2005,16 +1348,16 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="R4" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="S4" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="T4" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="U4" s="0">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="V4" s="0">
         <x:v>10</x:v>
@@ -2119,7 +1462,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="BE4" s="0">
-        <x:v>0.300000011920929</x:v>
+        <x:v>1.64999997615814</x:v>
       </x:c>
       <x:c r="BF4" s="0">
         <x:v>9999</x:v>
@@ -2128,16 +1471,16 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="BH4" s="0">
-        <x:v>0.300000011920929</x:v>
+        <x:v>1.64999997615814</x:v>
       </x:c>
       <x:c r="BI4" s="0">
-        <x:v>2</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="BJ4" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="BK4" s="0">
-        <x:v>1829</x:v>
+        <x:v>1845</x:v>
       </x:c>
       <x:c r="BL4" s="0">
         <x:v>0</x:v>
@@ -2146,16 +1489,16 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="BN4" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="BO4" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="BP4" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="BQ4" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="BR4" s="0">
         <x:v>1</x:v>
@@ -2173,19 +1516,40 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="BW4" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="BX4" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="BY4" s="1">
-        <x:v>45329.0995591551</x:v>
+        <x:v>45329.4402279977</x:v>
       </x:c>
       <x:c r="BZ4" s="1">
-        <x:v>45329.0995591551</x:v>
+        <x:v>45329.4402279977</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:78">
+      <x:c r="A5" s="0">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B5" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="C5" s="0" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="D5" s="0" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="E5" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="G5" s="0">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="H5" s="0">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="P5" s="0">
         <x:v>0</x:v>
       </x:c>
@@ -2193,16 +1557,16 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="R5" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="S5" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="T5" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="U5" s="0">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="V5" s="0">
         <x:v>10</x:v>
@@ -2259,7 +1623,7 @@
         <x:v>9999</x:v>
       </x:c>
       <x:c r="AO5" s="0">
-        <x:v>0.119999997317791</x:v>
+        <x:v>0.129999995231628</x:v>
       </x:c>
       <x:c r="AP5" s="0">
         <x:v>1800</x:v>
@@ -2307,7 +1671,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="BE5" s="0">
-        <x:v>0.300000011920929</x:v>
+        <x:v>1.64999997615814</x:v>
       </x:c>
       <x:c r="BF5" s="0">
         <x:v>9999</x:v>
@@ -2316,16 +1680,16 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="BH5" s="0">
-        <x:v>0.300000011920929</x:v>
+        <x:v>1.64999997615814</x:v>
       </x:c>
       <x:c r="BI5" s="0">
-        <x:v>2</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="BJ5" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="BK5" s="0">
-        <x:v>1830</x:v>
+        <x:v>1846</x:v>
       </x:c>
       <x:c r="BL5" s="0">
         <x:v>0</x:v>
@@ -2334,16 +1698,16 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="BN5" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="BO5" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="BP5" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="BQ5" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="BR5" s="0">
         <x:v>1</x:v>
@@ -2361,19 +1725,40 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="BW5" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="BX5" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="BY5" s="1">
-        <x:v>45329.0995751968</x:v>
+        <x:v>45329.4402493171</x:v>
       </x:c>
       <x:c r="BZ5" s="1">
-        <x:v>45329.0995751968</x:v>
+        <x:v>45329.4402493171</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:78">
+      <x:c r="A6" s="0">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B6" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="C6" s="0" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="D6" s="0" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="E6" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="G6" s="0">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="H6" s="0">
+        <x:v>2</x:v>
+      </x:c>
       <x:c r="P6" s="0">
         <x:v>0</x:v>
       </x:c>
@@ -2381,10 +1766,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="R6" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="S6" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="T6" s="0">
         <x:v>0</x:v>
@@ -2447,7 +1832,7 @@
         <x:v>9999</x:v>
       </x:c>
       <x:c r="AO6" s="0">
-        <x:v>0.119999997317791</x:v>
+        <x:v>0.129999995231628</x:v>
       </x:c>
       <x:c r="AP6" s="0">
         <x:v>1800</x:v>
@@ -2513,7 +1898,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="BK6" s="0">
-        <x:v>1835</x:v>
+        <x:v>1847</x:v>
       </x:c>
       <x:c r="BL6" s="0">
         <x:v>0</x:v>
@@ -2522,16 +1907,16 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="BN6" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="BO6" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="BP6" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="BQ6" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="BR6" s="0">
         <x:v>1</x:v>
@@ -2549,19 +1934,40 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="BW6" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="BX6" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="BY6" s="1">
-        <x:v>45329.1033836343</x:v>
+        <x:v>45329.4402686458</x:v>
       </x:c>
       <x:c r="BZ6" s="1">
-        <x:v>45329.1033836343</x:v>
+        <x:v>45329.4402686458</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:78">
+      <x:c r="A7" s="0">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B7" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="C7" s="0" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="D7" s="0" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="E7" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="G7" s="0">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="H7" s="0">
+        <x:v>3</x:v>
+      </x:c>
       <x:c r="P7" s="0">
         <x:v>0</x:v>
       </x:c>
@@ -2569,16 +1975,16 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="R7" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="S7" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="T7" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="U7" s="0">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="V7" s="0">
         <x:v>10</x:v>
@@ -2683,7 +2089,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="BE7" s="0">
-        <x:v>1.64999997615814</x:v>
+        <x:v>0.300000011920929</x:v>
       </x:c>
       <x:c r="BF7" s="0">
         <x:v>9999</x:v>
@@ -2692,16 +2098,16 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="BH7" s="0">
-        <x:v>1.64999997615814</x:v>
+        <x:v>0.300000011920929</x:v>
       </x:c>
       <x:c r="BI7" s="0">
-        <x:v>11</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="BJ7" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="BK7" s="0">
-        <x:v>1836</x:v>
+        <x:v>1848</x:v>
       </x:c>
       <x:c r="BL7" s="0">
         <x:v>0</x:v>
@@ -2710,16 +2116,16 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="BN7" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="BO7" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="BP7" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="BQ7" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="BR7" s="0">
         <x:v>1</x:v>
@@ -2737,19 +2143,40 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="BW7" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="BX7" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="BY7" s="1">
-        <x:v>45329.1033963657</x:v>
+        <x:v>45329.4402893056</x:v>
       </x:c>
       <x:c r="BZ7" s="1">
-        <x:v>45329.1033963657</x:v>
+        <x:v>45329.4402893056</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:78">
+      <x:c r="A8" s="0">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B8" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="C8" s="0" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="D8" s="0" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="E8" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="G8" s="0">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="H8" s="0">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="P8" s="0">
         <x:v>0</x:v>
       </x:c>
@@ -2757,10 +2184,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="R8" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="S8" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="T8" s="0">
         <x:v>0</x:v>
@@ -2823,7 +2250,7 @@
         <x:v>9999</x:v>
       </x:c>
       <x:c r="AO8" s="0">
-        <x:v>0.119999997317791</x:v>
+        <x:v>0.140000000596046</x:v>
       </x:c>
       <x:c r="AP8" s="0">
         <x:v>1800</x:v>
@@ -2889,7 +2316,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="BK8" s="0">
-        <x:v>1837</x:v>
+        <x:v>1849</x:v>
       </x:c>
       <x:c r="BL8" s="0">
         <x:v>0</x:v>
@@ -2898,10 +2325,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="BN8" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="BO8" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="BP8" s="0" t="s">
         <x:v>85</x:v>
@@ -2925,1046 +2352,22 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="BW8" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="BX8" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="BY8" s="1">
-        <x:v>45329.1034094676</x:v>
+        <x:v>45329.4403335301</x:v>
       </x:c>
       <x:c r="BZ8" s="1">
-        <x:v>45329.1034094676</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:78">
-      <x:c r="P9" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Q9" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="R9" s="0" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="S9" s="0" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="T9" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="U9" s="0">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="V9" s="0">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="W9" s="0">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="X9" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Y9" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Z9" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AA9" s="0">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="AB9" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AC9" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AD9" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AE9" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AG9" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AH9" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AI9" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AJ9" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AK9" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AL9" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AM9" s="0">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="AN9" s="0">
-        <x:v>9999</x:v>
-      </x:c>
-      <x:c r="AO9" s="0">
-        <x:v>0.119999997317791</x:v>
-      </x:c>
-      <x:c r="AP9" s="0">
-        <x:v>1800</x:v>
-      </x:c>
-      <x:c r="AQ9" s="0">
-        <x:v>2200</x:v>
-      </x:c>
-      <x:c r="AR9" s="0">
-        <x:v>2000</x:v>
-      </x:c>
-      <x:c r="AS9" s="0">
-        <x:v>1999</x:v>
-      </x:c>
-      <x:c r="AT9" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AU9" s="0">
-        <x:v>9999</x:v>
-      </x:c>
-      <x:c r="AV9" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AW9" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AX9" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AY9" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AZ9" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA9" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BB9" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BC9" s="0">
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="BD9" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BE9" s="0">
-        <x:v>0.300000011920929</x:v>
-      </x:c>
-      <x:c r="BF9" s="0">
-        <x:v>9999</x:v>
-      </x:c>
-      <x:c r="BG9" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BH9" s="0">
-        <x:v>0.300000011920929</x:v>
-      </x:c>
-      <x:c r="BI9" s="0">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="BJ9" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BK9" s="0">
-        <x:v>1838</x:v>
-      </x:c>
-      <x:c r="BL9" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BM9" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BN9" s="0" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="BO9" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="BP9" s="0" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="BQ9" s="0" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="BR9" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BS9" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BT9" s="0">
-        <x:v>-1</x:v>
-      </x:c>
-      <x:c r="BU9" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BV9" s="0">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="BW9" s="0" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="BX9" s="0" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="BY9" s="1">
-        <x:v>45329.1034237153</x:v>
-      </x:c>
-      <x:c r="BZ9" s="1">
-        <x:v>45329.1034237153</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:78">
-      <x:c r="A10" s="0">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="B10" s="0" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="C10" s="0" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="D10" s="0" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="E10" s="0" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="G10" s="0">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="H10" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="P10" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Q10" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="R10" s="0" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="S10" s="0" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="T10" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="U10" s="0">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="V10" s="0">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="W10" s="0">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="X10" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Y10" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Z10" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AA10" s="0">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="AB10" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AC10" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AD10" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AE10" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AG10" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AH10" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AI10" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AJ10" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AK10" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AL10" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AM10" s="0">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="AN10" s="0">
-        <x:v>9999</x:v>
-      </x:c>
-      <x:c r="AO10" s="0">
-        <x:v>0.109999999403954</x:v>
-      </x:c>
-      <x:c r="AP10" s="0">
-        <x:v>1800</x:v>
-      </x:c>
-      <x:c r="AQ10" s="0">
-        <x:v>2200</x:v>
-      </x:c>
-      <x:c r="AR10" s="0">
-        <x:v>2000</x:v>
-      </x:c>
-      <x:c r="AS10" s="0">
-        <x:v>1999</x:v>
-      </x:c>
-      <x:c r="AT10" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AU10" s="0">
-        <x:v>9999</x:v>
-      </x:c>
-      <x:c r="AV10" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AW10" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AX10" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AY10" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AZ10" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA10" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BB10" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BC10" s="0">
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="BD10" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BE10" s="0">
-        <x:v>1.64999997615814</x:v>
-      </x:c>
-      <x:c r="BF10" s="0">
-        <x:v>9999</x:v>
-      </x:c>
-      <x:c r="BG10" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BH10" s="0">
-        <x:v>1.64999997615814</x:v>
-      </x:c>
-      <x:c r="BI10" s="0">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="BJ10" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BK10" s="0">
-        <x:v>1839</x:v>
-      </x:c>
-      <x:c r="BL10" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BM10" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BN10" s="0" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="BO10" s="0" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="BP10" s="0" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="BQ10" s="0" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="BR10" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BS10" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BT10" s="0">
-        <x:v>-1</x:v>
-      </x:c>
-      <x:c r="BU10" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BV10" s="0">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="BW10" s="0" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="BX10" s="0" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="BY10" s="1">
-        <x:v>45329.1152479051</x:v>
-      </x:c>
-      <x:c r="BZ10" s="1">
-        <x:v>45329.1152479051</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:78">
-      <x:c r="A11" s="0">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="B11" s="0" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="C11" s="0" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="D11" s="0" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="E11" s="0" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="G11" s="0">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="H11" s="0">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="P11" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Q11" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="R11" s="0" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="S11" s="0" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="T11" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="U11" s="0">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="V11" s="0">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="W11" s="0">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="X11" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Y11" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Z11" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AA11" s="0">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="AB11" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AC11" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AD11" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AE11" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AG11" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AH11" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AI11" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AJ11" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AK11" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AL11" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AM11" s="0">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="AN11" s="0">
-        <x:v>9999</x:v>
-      </x:c>
-      <x:c r="AO11" s="0">
-        <x:v>0.129999995231628</x:v>
-      </x:c>
-      <x:c r="AP11" s="0">
-        <x:v>1800</x:v>
-      </x:c>
-      <x:c r="AQ11" s="0">
-        <x:v>2200</x:v>
-      </x:c>
-      <x:c r="AR11" s="0">
-        <x:v>2000</x:v>
-      </x:c>
-      <x:c r="AS11" s="0">
-        <x:v>1999</x:v>
-      </x:c>
-      <x:c r="AT11" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AU11" s="0">
-        <x:v>9999</x:v>
-      </x:c>
-      <x:c r="AV11" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AW11" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AX11" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AY11" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AZ11" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA11" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BB11" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BC11" s="0">
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="BD11" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BE11" s="0">
-        <x:v>1.64999997615814</x:v>
-      </x:c>
-      <x:c r="BF11" s="0">
-        <x:v>9999</x:v>
-      </x:c>
-      <x:c r="BG11" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BH11" s="0">
-        <x:v>1.64999997615814</x:v>
-      </x:c>
-      <x:c r="BI11" s="0">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="BJ11" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BK11" s="0">
-        <x:v>1840</x:v>
-      </x:c>
-      <x:c r="BL11" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BM11" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BN11" s="0" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="BO11" s="0" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="BP11" s="0" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="BQ11" s="0" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="BR11" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BS11" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BT11" s="0">
-        <x:v>-1</x:v>
-      </x:c>
-      <x:c r="BU11" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BV11" s="0">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="BW11" s="0" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="BX11" s="0" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="BY11" s="1">
-        <x:v>45329.1152629051</x:v>
-      </x:c>
-      <x:c r="BZ11" s="1">
-        <x:v>45329.1152629051</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:78">
-      <x:c r="A12" s="0">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="B12" s="0" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="C12" s="0" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="D12" s="0" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="E12" s="0" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="G12" s="0">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="H12" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="P12" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Q12" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="R12" s="0" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="S12" s="0" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="T12" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="U12" s="0">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="V12" s="0">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="W12" s="0">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="X12" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Y12" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Z12" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AA12" s="0">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="AB12" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AC12" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AD12" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AE12" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AG12" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AH12" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AI12" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AJ12" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AK12" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AL12" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AM12" s="0">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="AN12" s="0">
-        <x:v>9999</x:v>
-      </x:c>
-      <x:c r="AO12" s="0">
-        <x:v>0.119999997317791</x:v>
-      </x:c>
-      <x:c r="AP12" s="0">
-        <x:v>1800</x:v>
-      </x:c>
-      <x:c r="AQ12" s="0">
-        <x:v>2200</x:v>
-      </x:c>
-      <x:c r="AR12" s="0">
-        <x:v>2000</x:v>
-      </x:c>
-      <x:c r="AS12" s="0">
-        <x:v>1999</x:v>
-      </x:c>
-      <x:c r="AT12" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AU12" s="0">
-        <x:v>9999</x:v>
-      </x:c>
-      <x:c r="AV12" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AW12" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AX12" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AY12" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AZ12" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA12" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BB12" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BC12" s="0">
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="BD12" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BE12" s="0">
-        <x:v>0.300000011920929</x:v>
-      </x:c>
-      <x:c r="BF12" s="0">
-        <x:v>9999</x:v>
-      </x:c>
-      <x:c r="BG12" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BH12" s="0">
-        <x:v>0.300000011920929</x:v>
-      </x:c>
-      <x:c r="BI12" s="0">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="BJ12" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BK12" s="0">
-        <x:v>1841</x:v>
-      </x:c>
-      <x:c r="BL12" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BM12" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BN12" s="0" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="BO12" s="0" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="BP12" s="0" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="BQ12" s="0" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="BR12" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BS12" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BT12" s="0">
-        <x:v>-1</x:v>
-      </x:c>
-      <x:c r="BU12" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BV12" s="0">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="BW12" s="0" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="BX12" s="0" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="BY12" s="1">
-        <x:v>45329.1152768287</x:v>
-      </x:c>
-      <x:c r="BZ12" s="1">
-        <x:v>45329.1152768287</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:78">
-      <x:c r="A13" s="0">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="B13" s="0" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="C13" s="0" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="D13" s="0" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="E13" s="0" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="G13" s="0">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="H13" s="0">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="P13" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Q13" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="R13" s="0" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="S13" s="0" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="T13" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="U13" s="0">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="V13" s="0">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="W13" s="0">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="X13" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Y13" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Z13" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AA13" s="0">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="AB13" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AC13" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AD13" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AE13" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AG13" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AH13" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AI13" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AJ13" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AK13" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AL13" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AM13" s="0">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="AN13" s="0">
-        <x:v>9999</x:v>
-      </x:c>
-      <x:c r="AO13" s="0">
-        <x:v>0.129999995231628</x:v>
-      </x:c>
-      <x:c r="AP13" s="0">
-        <x:v>1800</x:v>
-      </x:c>
-      <x:c r="AQ13" s="0">
-        <x:v>2200</x:v>
-      </x:c>
-      <x:c r="AR13" s="0">
-        <x:v>2000</x:v>
-      </x:c>
-      <x:c r="AS13" s="0">
-        <x:v>1999</x:v>
-      </x:c>
-      <x:c r="AT13" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AU13" s="0">
-        <x:v>9999</x:v>
-      </x:c>
-      <x:c r="AV13" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AW13" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AX13" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AY13" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AZ13" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA13" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BB13" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BC13" s="0">
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="BD13" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BE13" s="0">
-        <x:v>0.300000011920929</x:v>
-      </x:c>
-      <x:c r="BF13" s="0">
-        <x:v>9999</x:v>
-      </x:c>
-      <x:c r="BG13" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BH13" s="0">
-        <x:v>0.300000011920929</x:v>
-      </x:c>
-      <x:c r="BI13" s="0">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="BJ13" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BK13" s="0">
-        <x:v>1842</x:v>
-      </x:c>
-      <x:c r="BL13" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BM13" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BN13" s="0" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="BO13" s="0" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="BP13" s="0" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="BQ13" s="0" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="BR13" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BS13" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BT13" s="0">
-        <x:v>-1</x:v>
-      </x:c>
-      <x:c r="BU13" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BV13" s="0">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="BW13" s="0" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="BX13" s="0" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="BY13" s="1">
-        <x:v>45329.1152912153</x:v>
-      </x:c>
-      <x:c r="BZ13" s="1">
-        <x:v>45329.1152912153</x:v>
+        <x:v>45329.4403335301</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="portrait" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
+  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
   <x:headerFooter/>
   <x:tableParts count="0"/>
 </x:worksheet>
